--- a/output/pdf_financials_xlsx/VCG.xlsx
+++ b/output/pdf_financials_xlsx/VCG.xlsx
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-2.242198</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-3.626157</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>-2.930781</v>
@@ -19538,7 +19538,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VCG.xlsx
+++ b/output/pdf_financials_xlsx/VCG.xlsx
@@ -969,16 +969,16 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000309</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.001068</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.001676</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.001019</v>
       </c>
     </row>
     <row r="13">
@@ -1764,16 +1764,16 @@
         <v>-0.902081</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.577042</v>
+        <v>1.576733</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.76849</v>
+        <v>-0.769558</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.859968</v>
+        <v>-0.861644</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.9956159999999999</v>
+        <v>-0.996635</v>
       </c>
     </row>
     <row r="28">
@@ -1862,16 +1862,16 @@
         <v>-0.832965</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.642876</v>
+        <v>1.642567</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.704202</v>
+        <v>-0.70527</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.837722</v>
+        <v>-0.839398</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.97631</v>
+        <v>-0.977329</v>
       </c>
     </row>
     <row r="30">
@@ -6599,19 +6599,19 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.062102</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.055914</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.063566</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.063592</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.005301</v>
       </c>
       <c r="O124" s="3" t="n">
         <v>0</v>
@@ -6650,19 +6650,19 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.062102</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.055914</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.063566</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.063592</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.005301</v>
       </c>
       <c r="O125" s="3" t="n">
         <v>0</v>
@@ -15304,7 +15304,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -24254,7 +24258,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">

--- a/output/pdf_financials_xlsx/VCG.xlsx
+++ b/output/pdf_financials_xlsx/VCG.xlsx
@@ -5996,10 +5996,10 @@
         <v>0</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.001659</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.008623</v>
       </c>
       <c r="O112" s="3" t="n">
         <v>0</v>
@@ -14314,7 +14314,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -16144,7 +16148,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VCG.xlsx
+++ b/output/pdf_financials_xlsx/VCG.xlsx
@@ -1141,10 +1141,10 @@
         <v>-2.794972</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-17.194821</v>
+        <v>-11.344821</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-4.389963</v>
+        <v>-3.971657</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-1.983638</v>
@@ -1184,16 +1184,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1.196</v>
+        <v>-1.196</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.008092999999999999</v>
+        <v>-0.008092999999999999</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-5.85</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.418306</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1214,7 +1214,7 @@
         <v>0.25</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-1.535991</v>
+        <v>1.535991</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>0.507831</v>
@@ -1223,7 +1223,7 @@
         <v>0.141447</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>0.077723</v>
+        <v>-0.077723</v>
       </c>
     </row>
     <row r="18">
@@ -1740,10 +1740,10 @@
         <v>-2.842466</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-17.224788</v>
+        <v>-11.374788</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.393097</v>
+        <v>-3.974791</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.989833</v>
@@ -1792,7 +1792,7 @@
         <v>0.02934</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.023149</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0.00971</v>
@@ -1838,10 +1838,10 @@
         <v>-2.80881</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-17.195448</v>
+        <v>-11.345448</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.393097</v>
+        <v>-3.951642</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.980123</v>
@@ -1964,10 +1964,10 @@
         <v>-0.2895556735452091</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-51.56537948020511</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-10.5322790966088</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -3601,34 +3601,34 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.167691</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.367674</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.29246</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.128455</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.469854</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>1.029532</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.601987</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.372184</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>1.074178</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.9486019999999999</v>
       </c>
     </row>
     <row r="65">
@@ -3748,34 +3748,34 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.068534</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.133044</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.042933</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.042934</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.058997</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.042928</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.057393</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.046364</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.059109</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.555112</v>
       </c>
     </row>
     <row r="68">
@@ -5306,10 +5306,8 @@
       <c r="D99" s="3" t="n">
         <v>-17.194821</v>
       </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E99" s="3" t="n">
+        <v>-4.389963</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>-1.983638</v>
@@ -5357,10 +5355,8 @@
       <c r="D100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -5408,10 +5404,8 @@
       <c r="D101" s="3" t="n">
         <v>-0.002257</v>
       </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E101" s="3" t="n">
+        <v>-0.010405</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>-0.008525</v>
@@ -5459,10 +5453,8 @@
       <c r="D102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="3" t="n">
         <v>0</v>
@@ -5510,10 +5502,8 @@
       <c r="D103" s="3" t="n">
         <v>0.012745</v>
       </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E103" s="3" t="n">
+        <v>-0.088801</v>
       </c>
       <c r="F103" s="3" t="n">
         <v>-0.015638</v>
@@ -5561,10 +5551,8 @@
       <c r="D104" s="3" t="n">
         <v>-9.399999999999999e-05</v>
       </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E104" s="3" t="n">
+        <v>-0.037581</v>
       </c>
       <c r="F104" s="3" t="n">
         <v>0.01114</v>
@@ -5612,10 +5600,8 @@
       <c r="D105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F105" s="3" t="n">
         <v>0</v>
@@ -5663,10 +5649,8 @@
       <c r="D106" s="3" t="n">
         <v>-1.118584</v>
       </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E106" s="3" t="n">
+        <v>-1.147656</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>-1.525412</v>
@@ -5714,10 +5698,8 @@
       <c r="D107" s="3" t="n">
         <v>0.347878</v>
       </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E107" s="3" t="n">
+        <v>0.205781</v>
       </c>
       <c r="F107" s="3" t="n">
         <v>0.461539</v>
@@ -5765,10 +5747,8 @@
       <c r="D108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="3" t="n">
         <v>0</v>
@@ -5816,10 +5796,8 @@
       <c r="D109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F109" s="3" t="n">
         <v>0</v>
@@ -5867,10 +5845,8 @@
       <c r="D110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -5913,15 +5889,13 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.011395</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.027396</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -5969,10 +5943,8 @@
       <c r="D112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -6020,10 +5992,8 @@
       <c r="D113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="3" t="n">
         <v>0</v>
@@ -6071,10 +6041,8 @@
       <c r="D114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="3" t="n">
         <v>0</v>
@@ -6122,10 +6090,8 @@
       <c r="D115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -6134,10 +6100,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.100229</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.108605</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -6173,10 +6139,8 @@
       <c r="D116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
         <v>0</v>
@@ -6224,10 +6188,8 @@
       <c r="D117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="3" t="n">
         <v>0</v>
@@ -6275,10 +6237,8 @@
       <c r="D118" s="3" t="n">
         <v>20.235034</v>
       </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E118" s="3" t="n">
+        <v>3.324238</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>-2.242198</v>
@@ -6326,10 +6286,8 @@
       <c r="D119" s="3" t="n">
         <v>-1.340921</v>
       </c>
-      <c r="E119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E119" s="3" t="n">
+        <v>-0.222427</v>
       </c>
       <c r="F119" s="3" t="n">
         <v>-2.087198</v>
@@ -6377,10 +6335,8 @@
       <c r="D120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
@@ -6428,10 +6384,8 @@
       <c r="D121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="3" t="n">
         <v>0</v>
@@ -6479,10 +6433,8 @@
       <c r="D122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F122" s="3" t="n">
         <v>0</v>
@@ -6530,10 +6482,8 @@
       <c r="D123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="3" t="n">
         <v>0</v>
@@ -6581,10 +6531,8 @@
       <c r="D124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>0</v>
@@ -6632,10 +6580,8 @@
       <c r="D125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>0</v>
@@ -6683,10 +6629,8 @@
       <c r="D126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="3" t="n">
         <v>0</v>
@@ -6811,10 +6755,8 @@
       <c r="D128" s="3" t="n">
         <v>0.378618</v>
       </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E128" s="3" t="n">
+        <v>-0.032272</v>
       </c>
       <c r="F128" s="3" t="n">
         <v>-0.099108</v>
@@ -6862,10 +6804,8 @@
       <c r="D129" s="3" t="n">
         <v>0.378618</v>
       </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E129" s="3" t="n">
+        <v>4.072103</v>
       </c>
       <c r="F129" s="3" t="n">
         <v>4.208892</v>
@@ -6913,10 +6853,8 @@
       <c r="D130" s="3" t="n">
         <v>3.04237</v>
       </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E130" s="3" t="n">
+        <v>0.961483</v>
       </c>
       <c r="F130" s="3" t="n">
         <v>3.663503</v>
@@ -6964,10 +6902,8 @@
       <c r="D131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="3" t="n">
         <v>0</v>
@@ -7015,10 +6951,8 @@
       <c r="D132" s="3" t="n">
         <v>-2.080887</v>
       </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E132" s="3" t="n">
+        <v>2.70202</v>
       </c>
       <c r="F132" s="3" t="n">
         <v>0.596282</v>
@@ -7066,10 +7000,8 @@
       <c r="D133" s="3" t="n">
         <v>0.961483</v>
       </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E133" s="3" t="n">
+        <v>3.663503</v>
       </c>
       <c r="F133" s="3" t="n">
         <v>4.259785</v>
@@ -7112,15 +7044,13 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.011395</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.027396</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -7163,15 +7093,13 @@
         <v>-1.349102</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.268143</v>
+        <v>-1.279538</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.118584</v>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.14598</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-1.152656</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-1.525412</v>
@@ -7215,7 +7143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R332"/>
+  <dimension ref="A1:R333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13858,10 +13786,8 @@
       <c r="G80" s="5" t="n">
         <v>0.02934</v>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H80" s="5" t="n">
+        <v>0.023149</v>
       </c>
       <c r="I80" s="5" t="n">
         <v>0.00971</v>
@@ -14592,10 +14518,8 @@
       <c r="G89" s="5" t="n">
         <v>-9.399999999999999e-05</v>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H89" s="5" t="n">
+        <v>-0.037581</v>
       </c>
       <c r="I89" s="5" t="n">
         <v>0.15334</v>
@@ -15168,10 +15092,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H96" s="5" t="n">
+        <v>-0.032272</v>
       </c>
       <c r="I96" s="5" t="n">
         <v>-0.099108</v>
@@ -15576,10 +15498,8 @@
       <c r="G101" s="5" t="n">
         <v>3.04237</v>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H101" s="5" t="n">
+        <v>0.961483</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -15646,10 +15566,8 @@
       <c r="G102" s="5" t="n">
         <v>0.961483</v>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H102" s="5" t="n">
+        <v>3.663503</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -15712,10 +15630,8 @@
       <c r="G103" s="5" t="n">
         <v>0.106483</v>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H103" s="5" t="n">
+        <v>3.663503</v>
       </c>
       <c r="I103" s="5" t="n">
         <v>1.476785</v>
@@ -16340,10 +16256,8 @@
       <c r="G111" s="5" t="n">
         <v>0.012745</v>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H111" s="5" t="n">
+        <v>-0.088801</v>
       </c>
       <c r="I111" s="5" t="n">
         <v>-0.015638</v>
@@ -17271,15 +17185,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G122" s="5" t="n">
+        <v>-2.080887</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>2.70202</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -18198,7 +18108,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -18730,10 +18644,8 @@
       <c r="G139" s="5" t="n">
         <v>-0.002257</v>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H139" s="5" t="n">
+        <v>-0.010405</v>
       </c>
       <c r="I139" s="5" t="n">
         <v>-0.008525</v>
@@ -18812,10 +18724,8 @@
       <c r="G140" s="5" t="n">
         <v>-1.118584</v>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H140" s="5" t="n">
+        <v>-1.147656</v>
       </c>
       <c r="I140" s="5" t="n">
         <v>-1.525412</v>
@@ -19046,7 +18956,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -19146,10 +19060,8 @@
       <c r="G144" s="5" t="n">
         <v>-1.340921</v>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H144" s="5" t="n">
+        <v>-0.222427</v>
       </c>
       <c r="I144" s="5" t="n">
         <v>-2.087198</v>
@@ -19312,10 +19224,8 @@
       <c r="G146" s="5" t="n">
         <v>0.378618</v>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H146" s="5" t="n">
+        <v>4.072103</v>
       </c>
       <c r="I146" s="5" t="n">
         <v>4.208892</v>
@@ -19565,15 +19475,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G149" s="5" t="n">
+        <v>-1.290823</v>
+      </c>
+      <c r="H149" s="5" t="n">
+        <v>-0.212137</v>
       </c>
       <c r="I149" s="5" t="n">
         <v>-2.242198</v>
@@ -19731,15 +19637,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G151" s="5" t="n">
+        <v>0.378618</v>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>4.104375</v>
       </c>
       <c r="I151" s="5" t="n">
         <v>4.308</v>
@@ -20596,10 +20498,8 @@
       <c r="G161" s="5" t="n">
         <v>-17.194821</v>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H161" s="5" t="n">
+        <v>-4.389963</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -20684,10 +20584,8 @@
       <c r="G162" s="5" t="n">
         <v>0.347878</v>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H162" s="5" t="n">
+        <v>0.205781</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -20753,29 +20651,25 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Write off and impairment of exploration and evaluation assets</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Write off of equipment</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F163" s="5" t="n">
-        <v>1.122556</v>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>21.525857</v>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00552</v>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>0.032095</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -20841,10 +20735,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Write off of equipment</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>Impairment of exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -20856,12 +20754,10 @@
         </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.00552</v>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>21.525857</v>
+      </c>
+      <c r="H164" s="5" t="n">
+        <v>3.536375</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -20930,7 +20826,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -20942,10 +20842,8 @@
       <c r="G165" s="5" t="n">
         <v>-5.85</v>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H165" s="5" t="n">
+        <v>-0.418306</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -21095,12 +20993,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Acquisition of exploration and evaluation assets</t>
+          <t>Purchase of equipment</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>PurchaseOfPPE</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -21109,15 +21007,13 @@
         </is>
       </c>
       <c r="F167" s="5" t="n">
-        <v>-2.382297</v>
+        <v>-0.011395</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>-1.290823</v>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.027396</v>
+      </c>
+      <c r="H167" s="5" t="n">
+        <v>-0.005</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -21183,7 +21079,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Purchase of equipment</t>
+          <t>Deposits</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -21192,16 +21088,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F168" s="5" t="n">
-        <v>-0.011395</v>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G168" s="5" t="n">
-        <v>-0.027396</v>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.022702</v>
+      </c>
+      <c r="H168" s="5" t="n">
+        <v>-0.00529</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -21262,27 +21158,29 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Deposits</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
+          <t>Write off and impairment of exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F169" s="5" t="n">
+        <v>1.122556</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>-0.022702</v>
+        <v>21.525857</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -21348,17 +21246,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Proceeds on shares issued, net of share issuance costs</t>
+          <t>Acquisition of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -21367,10 +21265,10 @@
         </is>
       </c>
       <c r="F170" s="5" t="n">
-        <v>1.25635</v>
+        <v>-2.382297</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.378618</v>
+        <v>-1.290823</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -21441,22 +21339,24 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Subscriptions received in advance</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>Proceeds on shares issued, net of share issuance costs</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F171" s="5" t="n">
-        <v>0.38395</v>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.25635</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>0.378618</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -21522,12 +21422,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information -Note 14</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information -Note 14 of Total $</t>
+          <t>Subscriptions received in advance</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -21537,10 +21437,12 @@
         </is>
       </c>
       <c r="F172" s="5" t="n">
-        <v>2e-05</v>
-      </c>
-      <c r="G172" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.38395</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -21611,7 +21513,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Page 30,367,610 1,356,000 383,950 53,000 (99,650) 275,998 89,600 (2,786,879) 29,639,629 362,644 32,513 (46,094) 12,000 347,878</t>
+          <t>Supplemental cash flow information -Note 14 of Total $</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -21621,10 +21523,10 @@
         </is>
       </c>
       <c r="F173" s="5" t="n">
-        <v>13.163649</v>
+        <v>2e-05</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>-17.194821</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -21695,7 +21597,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Deficit $ (14,028,395) - - - - - - (2,786,879) (16,815,274) - - - - - -</t>
+          <t>Page 30,367,610 1,356,000 383,950 53,000 (99,650) 275,998 89,600 (2,786,879) 29,639,629 362,644 32,513 (46,094) 12,000 347,878</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -21705,7 +21607,7 @@
         </is>
       </c>
       <c r="F174" s="5" t="n">
-        <v>-34.010095</v>
+        <v>13.163649</v>
       </c>
       <c r="G174" s="5" t="n">
         <v>-17.194821</v>
@@ -21774,29 +21676,25 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>Supplemental cash flow information -Note 14</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Loss for the year $</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E175" s="5" t="n">
-        <v>-3.678895</v>
+          <t>Deficit $ (14,028,395) - - - - - - (2,786,879) (16,815,274) - - - - - -</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F175" s="5" t="n">
-        <v>-2.786879</v>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-34.010095</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>-17.194821</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -21862,24 +21760,24 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Equipment depreciation</t>
+          <t>Loss for the year $</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>0.027905</v>
+        <v>-3.678895</v>
       </c>
       <c r="F176" s="5" t="n">
-        <v>0.033656</v>
+        <v>-2.786879</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -21955,15 +21853,19 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Deferred income tax expense/(recovery)</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>Equipment depreciation</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E177" s="5" t="n">
-        <v>-1.196</v>
+        <v>0.027905</v>
       </c>
       <c r="F177" s="5" t="n">
-        <v>-0.008092999999999999</v>
+        <v>0.033656</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -22039,19 +21941,19 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Write-off exploration and evaluation assets</t>
+          <t>Deferred income tax expense/(recovery)</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>DeferredTax</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>2.982123</v>
+        <v>-1.196</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>1.122556</v>
+        <v>-0.008092999999999999</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -22122,20 +22024,24 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Decrease in receivable</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
+          <t>Write-off exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E179" s="5" t="n">
-        <v>0.361026</v>
+        <v>2.982123</v>
       </c>
       <c r="F179" s="5" t="n">
-        <v>0.131825</v>
+        <v>1.122556</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -22211,19 +22117,15 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Decrease in prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>Decrease in receivable</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" s="5" t="n">
-        <v>0.016483</v>
+        <v>0.361026</v>
       </c>
       <c r="F180" s="5" t="n">
-        <v>0.000652</v>
+        <v>0.131825</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -22299,15 +22201,19 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Decrease in deposits</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>Decrease in prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E181" s="5" t="n">
-        <v>0.191396</v>
+        <v>0.016483</v>
       </c>
       <c r="F181" s="5" t="n">
-        <v>0.103572</v>
+        <v>0.000652</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -22383,19 +22289,15 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Decrease in accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Decrease in deposits</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" s="5" t="n">
-        <v>-0.127703</v>
+        <v>0.191396</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>-0.14143</v>
+        <v>0.103572</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -22471,19 +22373,19 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Net cash (used in)/provided by operating activities</t>
+          <t>Decrease in accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E183" s="5" t="n">
-        <v>-1.349102</v>
+        <v>-0.127703</v>
       </c>
       <c r="F183" s="5" t="n">
-        <v>-1.268143</v>
+        <v>-0.14143</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -22554,24 +22456,24 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Acquisition of exploration and evaluation assets</t>
+          <t>Net cash (used in)/provided by operating activities</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>-5.475448</v>
+        <v>-1.349102</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>-2.382297</v>
+        <v>-1.268143</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -22647,15 +22549,19 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Equipment purchases</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>Acquisition of exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E185" s="5" t="n">
-        <v>-0.06310300000000001</v>
+        <v>-5.475448</v>
       </c>
       <c r="F185" s="5" t="n">
-        <v>-0.011395</v>
+        <v>-2.382297</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -22731,19 +22637,15 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Equipment purchases</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" s="5" t="n">
-        <v>-5.538551</v>
+        <v>-0.06310300000000001</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>-2.393692</v>
+        <v>-0.011395</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -22814,24 +22716,24 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Proceeds from the issuance of shares, net of share issuance costs</t>
+          <t>Net cash used in investing activities</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>1.480788</v>
+        <v>-5.538551</v>
       </c>
       <c r="F187" s="5" t="n">
-        <v>1.25635</v>
+        <v>-2.393692</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -22907,15 +22809,19 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Subscriptions received in advance</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr"/>
+          <t>Proceeds from the issuance of shares, net of share issuance costs</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E188" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.480788</v>
       </c>
       <c r="F188" s="5" t="n">
-        <v>0.38395</v>
+        <v>1.25635</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -22991,19 +22897,15 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Subscriptions received in advance</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
       <c r="E189" s="5" t="n">
-        <v>2.170788</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F189" s="5" t="n">
-        <v>1.6403</v>
+        <v>0.38395</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -23079,15 +22981,19 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Decrease in cash and cash equivalents for the year</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E190" s="5" t="n">
-        <v>-4.716865</v>
+        <v>2.170788</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>-2.021535</v>
+        <v>1.6403</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -23163,19 +23069,15 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Decrease in cash and cash equivalents for the year</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
       <c r="E191" s="5" t="n">
-        <v>9.78077</v>
+        <v>-4.716865</v>
       </c>
       <c r="F191" s="5" t="n">
-        <v>5.063905</v>
+        <v>-2.021535</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -23251,19 +23153,19 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year $</t>
+          <t>Cash and cash equivalents, beginning of year</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
+        <v>9.78077</v>
+      </c>
+      <c r="F192" s="5" t="n">
         <v>5.063905</v>
-      </c>
-      <c r="F192" s="5" t="n">
-        <v>3.04237</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -23339,19 +23241,19 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Cash paid during the year for interest $</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and cash equivalents, end of year $</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="n">
+        <v>5.063905</v>
+      </c>
+      <c r="F193" s="5" t="n">
+        <v>3.04237</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -23427,7 +23329,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Cash paid during the year for income taxes $</t>
+          <t>Cash paid during the year for interest $</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -23510,20 +23412,24 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents consist of</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Cash $</t>
+          <t>Cash paid during the year for income taxes $</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
-      <c r="E195" s="5" t="n">
-        <v>0.442039</v>
-      </c>
-      <c r="F195" s="5" t="n">
-        <v>0.47322</v>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -23599,15 +23505,15 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Cash equivalents $</t>
+          <t>Cash $</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" s="5" t="n">
-        <v>4.621866</v>
+        <v>0.442039</v>
       </c>
       <c r="F196" s="5" t="n">
-        <v>2.56915</v>
+        <v>0.47322</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -23673,25 +23579,25 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents consist of</t>
+        </is>
+      </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Corporate development</t>
+          <t>Cash equivalents $</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E197" s="5" t="n">
+        <v>4.621866</v>
+      </c>
+      <c r="F197" s="5" t="n">
+        <v>2.56915</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -23703,35 +23609,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I197" s="5" t="n">
-        <v>0.792296</v>
-      </c>
-      <c r="J197" s="5" t="n">
-        <v>0.825252</v>
-      </c>
-      <c r="K197" s="5" t="n">
-        <v>0.572712</v>
-      </c>
-      <c r="L197" s="5" t="n">
-        <v>0.213959</v>
-      </c>
-      <c r="M197" s="5" t="n">
-        <v>0.206072</v>
-      </c>
-      <c r="N197" s="5" t="n">
-        <v>0.72037</v>
-      </c>
-      <c r="O197" s="5" t="n">
-        <v>0.634439</v>
-      </c>
-      <c r="P197" s="5" t="n">
-        <v>1.19489</v>
-      </c>
-      <c r="Q197" s="5" t="n">
-        <v>0.364811</v>
-      </c>
-      <c r="R197" s="5" t="n">
-        <v>0.230853</v>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="198">
@@ -23743,67 +23669,59 @@
       <c r="B198" t="inlineStr"/>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Depreciation 6</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Corporate development</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F198" s="5" t="n">
-        <v>0.033656</v>
-      </c>
-      <c r="G198" s="5" t="n">
-        <v>0.02934</v>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I198" s="5" t="n">
+        <v>0.792296</v>
+      </c>
+      <c r="J198" s="5" t="n">
+        <v>0.825252</v>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>0.572712</v>
+      </c>
+      <c r="L198" s="5" t="n">
+        <v>0.213959</v>
       </c>
       <c r="M198" s="5" t="n">
-        <v>0.06674099999999999</v>
+        <v>0.206072</v>
       </c>
       <c r="N198" s="5" t="n">
-        <v>0.069116</v>
+        <v>0.72037</v>
       </c>
       <c r="O198" s="5" t="n">
-        <v>0.065834</v>
+        <v>0.634439</v>
       </c>
       <c r="P198" s="5" t="n">
-        <v>0.064288</v>
+        <v>1.19489</v>
       </c>
       <c r="Q198" s="5" t="n">
-        <v>0.022246</v>
+        <v>0.364811</v>
       </c>
       <c r="R198" s="5" t="n">
-        <v>0.019306</v>
+        <v>0.230853</v>
       </c>
     </row>
     <row r="199">
@@ -23815,12 +23733,12 @@
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Listing and filing fees</t>
+          <t>Depreciation 6</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -23828,50 +23746,54 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F199" s="5" t="n">
+        <v>0.033656</v>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>0.02934</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I199" s="5" t="n">
-        <v>0.056615</v>
-      </c>
-      <c r="J199" s="5" t="n">
-        <v>0.074323</v>
-      </c>
-      <c r="K199" s="5" t="n">
-        <v>0.087579</v>
-      </c>
-      <c r="L199" s="5" t="n">
-        <v>0.066902</v>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M199" s="5" t="n">
-        <v>0.024091</v>
+        <v>0.06674099999999999</v>
       </c>
       <c r="N199" s="5" t="n">
-        <v>0.049956</v>
+        <v>0.069116</v>
       </c>
       <c r="O199" s="5" t="n">
-        <v>0.072726</v>
+        <v>0.065834</v>
       </c>
       <c r="P199" s="5" t="n">
-        <v>0.084254</v>
+        <v>0.064288</v>
       </c>
       <c r="Q199" s="5" t="n">
-        <v>0.151651</v>
+        <v>0.022246</v>
       </c>
       <c r="R199" s="5" t="n">
-        <v>0.102903</v>
+        <v>0.019306</v>
       </c>
     </row>
     <row r="200">
@@ -23883,12 +23805,12 @@
       <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Management and consulting fees 13</t>
+          <t>Listing and filing fees</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -23911,39 +23833,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I200" s="5" t="n">
+        <v>0.056615</v>
       </c>
       <c r="J200" s="5" t="n">
-        <v>0.333329</v>
+        <v>0.074323</v>
       </c>
       <c r="K200" s="5" t="n">
-        <v>0.540197</v>
+        <v>0.087579</v>
       </c>
       <c r="L200" s="5" t="n">
-        <v>0.31031</v>
+        <v>0.066902</v>
       </c>
       <c r="M200" s="5" t="n">
-        <v>0.229154</v>
+        <v>0.024091</v>
       </c>
       <c r="N200" s="5" t="n">
-        <v>0.40474</v>
+        <v>0.049956</v>
       </c>
       <c r="O200" s="5" t="n">
-        <v>0.274702</v>
-      </c>
-      <c r="P200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.072726</v>
+      </c>
+      <c r="P200" s="5" t="n">
+        <v>0.084254</v>
       </c>
       <c r="Q200" s="5" t="n">
-        <v>0.258978</v>
+        <v>0.151651</v>
       </c>
       <c r="R200" s="5" t="n">
-        <v>0.275898</v>
+        <v>0.102903</v>
       </c>
     </row>
     <row r="201">
@@ -23955,10 +23873,14 @@
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Office, administration and other</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>Management and consulting fees 13</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -23984,42 +23906,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J201" s="5" t="n">
+        <v>0.333329</v>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>0.540197</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="M201" s="5" t="n">
+        <v>0.229154</v>
+      </c>
+      <c r="N201" s="5" t="n">
+        <v>0.40474</v>
       </c>
       <c r="O201" s="5" t="n">
-        <v>0.180116</v>
-      </c>
-      <c r="P201" s="5" t="n">
-        <v>0.32233</v>
+        <v>0.274702</v>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q201" s="5" t="n">
-        <v>0.283114</v>
+        <v>0.258978</v>
       </c>
       <c r="R201" s="5" t="n">
-        <v>0.219306</v>
+        <v>0.275898</v>
       </c>
     </row>
     <row r="202">
@@ -24031,14 +23945,10 @@
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Professional fees 13</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Office, administration and other</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -24064,34 +23974,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J202" s="5" t="n">
-        <v>0.130982</v>
-      </c>
-      <c r="K202" s="5" t="n">
-        <v>0.137664</v>
-      </c>
-      <c r="L202" s="5" t="n">
-        <v>0.135728</v>
-      </c>
-      <c r="M202" s="5" t="n">
-        <v>0.148938</v>
-      </c>
-      <c r="N202" s="5" t="n">
-        <v>0.196733</v>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O202" s="5" t="n">
-        <v>0.147139</v>
-      </c>
-      <c r="P202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.180116</v>
+      </c>
+      <c r="P202" s="5" t="n">
+        <v>0.32233</v>
       </c>
       <c r="Q202" s="5" t="n">
-        <v>0.327191</v>
+        <v>0.283114</v>
       </c>
       <c r="R202" s="5" t="n">
-        <v>0.16744</v>
+        <v>0.219306</v>
       </c>
     </row>
     <row r="203">
@@ -24103,10 +24021,14 @@
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Share-based compensation 12(c),13</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>Professional fees 13</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -24132,31 +24054,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J203" s="5" t="n">
+        <v>0.130982</v>
+      </c>
+      <c r="K203" s="5" t="n">
+        <v>0.137664</v>
+      </c>
+      <c r="L203" s="5" t="n">
+        <v>0.135728</v>
       </c>
       <c r="M203" s="5" t="n">
-        <v>0.207186</v>
+        <v>0.148938</v>
       </c>
       <c r="N203" s="5" t="n">
-        <v>1.004589</v>
-      </c>
-      <c r="O203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.196733</v>
+      </c>
+      <c r="O203" s="5" t="n">
+        <v>0.147139</v>
       </c>
       <c r="P203" t="inlineStr">
         <is>
@@ -24164,10 +24078,10 @@
         </is>
       </c>
       <c r="Q203" s="5" t="n">
-        <v>0.287835</v>
+        <v>0.327191</v>
       </c>
       <c r="R203" s="5" t="n">
-        <v>0.291871</v>
+        <v>0.16744</v>
       </c>
     </row>
     <row r="204">
@@ -24179,7 +24093,7 @@
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Lease finance charges</t>
+          <t>Share-based compensation 12(c),13</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -24223,15 +24137,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M204" s="5" t="n">
+        <v>0.207186</v>
+      </c>
+      <c r="N204" s="5" t="n">
+        <v>1.004589</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
@@ -24244,12 +24154,10 @@
         </is>
       </c>
       <c r="Q204" s="5" t="n">
-        <v>-8.7e-05</v>
-      </c>
-      <c r="R204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.287835</v>
+      </c>
+      <c r="R204" s="5" t="n">
+        <v>0.291871</v>
       </c>
     </row>
     <row r="205">
@@ -24261,14 +24169,10 @@
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Lease finance charges</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -24319,17 +24223,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O205" s="5" t="n">
-        <v>0.000309</v>
-      </c>
-      <c r="P205" s="5" t="n">
-        <v>0.001068</v>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q205" s="5" t="n">
-        <v>0.001676</v>
-      </c>
-      <c r="R205" s="5" t="n">
-        <v>0.001019</v>
+        <v>-8.7e-05</v>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="206">
@@ -24341,12 +24251,12 @@
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -24389,23 +24299,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M206" s="5" t="n">
-        <v>-3.4e-05</v>
-      </c>
-      <c r="N206" s="5" t="n">
-        <v>-0.006848</v>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O206" s="5" t="n">
-        <v>-0.008111</v>
+        <v>0.000309</v>
       </c>
       <c r="P206" s="5" t="n">
-        <v>-0.019584</v>
+        <v>0.001068</v>
       </c>
       <c r="Q206" s="5" t="n">
-        <v>-0.007261</v>
+        <v>0.001676</v>
       </c>
       <c r="R206" s="5" t="n">
-        <v>-0.001866</v>
+        <v>0.001019</v>
       </c>
     </row>
     <row r="207">
@@ -24417,7 +24331,7 @@
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Other income 6</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -24465,33 +24379,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M207" s="5" t="n">
+        <v>-3.4e-05</v>
+      </c>
+      <c r="N207" s="5" t="n">
+        <v>-0.006848</v>
+      </c>
+      <c r="O207" s="5" t="n">
+        <v>-0.008111</v>
+      </c>
+      <c r="P207" s="5" t="n">
+        <v>-0.019584</v>
+      </c>
+      <c r="Q207" s="5" t="n">
+        <v>-0.007261</v>
       </c>
       <c r="R207" s="5" t="n">
-        <v>0.23</v>
+        <v>-0.001866</v>
       </c>
     </row>
     <row r="208">
@@ -24503,10 +24407,14 @@
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Impairment of property and equipment 6</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
+          <t>Other income 6</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -24567,13 +24475,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q208" s="5" t="n">
-        <v>-0.008623</v>
-      </c>
-      <c r="R208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R208" s="5" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="209">
@@ -24585,7 +24493,7 @@
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Write-down of exploration and evaluation assets 7</t>
+          <t>Impairment of property and equipment 6</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -24634,8 +24542,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N209" s="5" t="n">
-        <v>-0.110018</v>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O209" t="inlineStr">
         <is>
@@ -24647,13 +24557,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R209" s="5" t="n">
-        <v>-0.02</v>
+      <c r="Q209" s="5" t="n">
+        <v>-0.008623</v>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -24665,7 +24575,7 @@
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Flow-through premium recovery 11</t>
+          <t>Write-down of exploration and evaluation assets 7</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -24699,35 +24609,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K210" s="5" t="n">
-        <v>0.154226</v>
-      </c>
-      <c r="L210" s="5" t="n">
-        <v>0.062488</v>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N210" s="5" t="n">
+        <v>-0.110018</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P210" s="5" t="n">
-        <v>2.133046</v>
-      </c>
-      <c r="Q210" s="5" t="n">
-        <v>0.850153</v>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R210" s="5" t="n">
-        <v>0.102808</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="211">
@@ -24739,14 +24655,10 @@
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Flow-through premium recovery 11</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -24777,21 +24689,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M211" s="5" t="n">
-        <v>-1.125121</v>
-      </c>
-      <c r="N211" s="5" t="n">
-        <v>-0.902081</v>
+      <c r="K211" s="5" t="n">
+        <v>0.154226</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>0.062488</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O211" t="inlineStr">
         <is>
@@ -24799,13 +24711,13 @@
         </is>
       </c>
       <c r="P211" s="5" t="n">
-        <v>-0.76849</v>
+        <v>2.133046</v>
       </c>
       <c r="Q211" s="5" t="n">
-        <v>-0.859968</v>
+        <v>0.850153</v>
       </c>
       <c r="R211" s="5" t="n">
-        <v>-0.9956159999999999</v>
+        <v>0.102808</v>
       </c>
     </row>
     <row r="212">
@@ -24817,10 +24729,14 @@
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense) 10</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr"/>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -24861,31 +24777,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M212" s="5" t="n">
+        <v>-1.125121</v>
+      </c>
+      <c r="N212" s="5" t="n">
+        <v>-0.902081</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P212" s="5" t="n">
+        <v>-0.76849</v>
       </c>
       <c r="Q212" s="5" t="n">
-        <v>-0.141447</v>
+        <v>-0.859968</v>
       </c>
       <c r="R212" s="5" t="n">
-        <v>0.077723</v>
+        <v>-0.9956159999999999</v>
       </c>
     </row>
     <row r="213">
@@ -24897,12 +24807,12 @@
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Loss and total comprehensive loss for the year</t>
+          <t>Income tax recovery (expense) 10</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -24945,11 +24855,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M213" s="5" t="n">
-        <v>-1.125121</v>
-      </c>
-      <c r="N213" s="5" t="n">
-        <v>-1.152081</v>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -24962,10 +24876,10 @@
         </is>
       </c>
       <c r="Q213" s="5" t="n">
-        <v>-1.001415</v>
+        <v>-0.141447</v>
       </c>
       <c r="R213" s="5" t="n">
-        <v>-0.917893</v>
+        <v>0.077723</v>
       </c>
     </row>
     <row r="214">
@@ -24974,19 +24888,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Loss per share</t>
-        </is>
-      </c>
+      <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr">
         <is>
-          <t>- Basic and diluted loss per share</t>
+          <t>Loss and total comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -25029,29 +24939,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M214" s="5" t="n">
+        <v>-1.125121</v>
+      </c>
+      <c r="N214" s="5" t="n">
+        <v>-1.152081</v>
       </c>
       <c r="O214" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P214" s="5" t="n">
-        <v>-8e-08</v>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q214" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>-1.001415</v>
       </c>
       <c r="R214" s="5" t="n">
-        <v>-5e-08</v>
+        <v>-0.917893</v>
       </c>
     </row>
     <row r="215">
@@ -25062,15 +24970,19 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>outstanding</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>- Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
+          <t>- Basic and diluted loss per share</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -25127,13 +25039,13 @@
         </is>
       </c>
       <c r="P215" s="5" t="n">
-        <v>16.258583</v>
+        <v>-8e-08</v>
       </c>
       <c r="Q215" s="5" t="n">
-        <v>17.674018</v>
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="R215" s="5" t="n">
-        <v>19.070486</v>
+        <v>-5e-08</v>
       </c>
     </row>
     <row r="216">
@@ -25142,17 +25054,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
+      </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Management and consulting fees 14</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>- Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -25203,19 +25115,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O216" s="5" t="n">
-        <v>0.274702</v>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P216" s="5" t="n">
-        <v>0.450524</v>
+        <v>16.258583</v>
       </c>
       <c r="Q216" s="5" t="n">
-        <v>0.258978</v>
-      </c>
-      <c r="R216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>17.674018</v>
+      </c>
+      <c r="R216" s="5" t="n">
+        <v>19.070486</v>
       </c>
     </row>
     <row r="217">
@@ -25227,12 +25139,12 @@
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Professional fees 14</t>
+          <t>Management and consulting fees 14</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -25286,13 +25198,13 @@
         </is>
       </c>
       <c r="O217" s="5" t="n">
-        <v>0.147139</v>
+        <v>0.274702</v>
       </c>
       <c r="P217" s="5" t="n">
-        <v>0.200778</v>
+        <v>0.450524</v>
       </c>
       <c r="Q217" s="5" t="n">
-        <v>0.327191</v>
+        <v>0.258978</v>
       </c>
       <c r="R217" t="inlineStr">
         <is>
@@ -25309,10 +25221,14 @@
       <c r="B218" t="inlineStr"/>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Share-based compensation 13(c),14</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr"/>
+          <t>Professional fees 14</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -25364,13 +25280,13 @@
         </is>
       </c>
       <c r="O218" s="5" t="n">
-        <v>0.354998</v>
+        <v>0.147139</v>
       </c>
       <c r="P218" s="5" t="n">
-        <v>0.556974</v>
+        <v>0.200778</v>
       </c>
       <c r="Q218" s="5" t="n">
-        <v>0.287835</v>
+        <v>0.327191</v>
       </c>
       <c r="R218" t="inlineStr">
         <is>
@@ -25387,7 +25303,7 @@
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Lease finance charges 8</t>
+          <t>Share-based compensation 13(c),14</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -25441,16 +25357,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O219" s="5" t="n">
+        <v>0.354998</v>
       </c>
       <c r="P219" s="5" t="n">
-        <v>-0.007323</v>
+        <v>0.556974</v>
       </c>
       <c r="Q219" s="5" t="n">
-        <v>-8.7e-05</v>
+        <v>0.287835</v>
       </c>
       <c r="R219" t="inlineStr">
         <is>
@@ -25467,7 +25381,7 @@
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Gain on disposal of property and equipment</t>
+          <t>Lease finance charges 8</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -25527,12 +25441,10 @@
         </is>
       </c>
       <c r="P220" s="5" t="n">
-        <v>-0.001659</v>
-      </c>
-      <c r="Q220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.007323</v>
+      </c>
+      <c r="Q220" s="5" t="n">
+        <v>-8.7e-05</v>
       </c>
       <c r="R220" t="inlineStr">
         <is>
@@ -25549,14 +25461,10 @@
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Income tax expense 10</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Gain on disposal of property and equipment</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -25613,10 +25521,12 @@
         </is>
       </c>
       <c r="P221" s="5" t="n">
-        <v>-0.507831</v>
-      </c>
-      <c r="Q221" s="5" t="n">
-        <v>-0.141447</v>
+        <v>-0.001659</v>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R221" t="inlineStr">
         <is>
@@ -25633,12 +25543,12 @@
       <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
+          <t>Income tax expense 10</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -25697,10 +25607,10 @@
         </is>
       </c>
       <c r="P222" s="5" t="n">
-        <v>-1.276321</v>
+        <v>-0.507831</v>
       </c>
       <c r="Q222" s="5" t="n">
-        <v>-1.001415</v>
+        <v>-0.141447</v>
       </c>
       <c r="R222" t="inlineStr">
         <is>
@@ -25717,10 +25627,14 @@
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Gain on sale of exploration asset 7</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -25771,18 +25685,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O223" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P223" s="5" t="n">
+        <v>-1.276321</v>
+      </c>
+      <c r="Q223" s="5" t="n">
+        <v>-1.001415</v>
       </c>
       <c r="R223" t="inlineStr">
         <is>
@@ -25799,7 +25711,7 @@
       <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Lease finance charges 9</t>
+          <t>Gain on sale of exploration asset 7</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -25843,17 +25755,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M224" s="5" t="n">
-        <v>-0.024429</v>
-      </c>
-      <c r="N224" s="5" t="n">
-        <v>-0.021824</v>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O224" s="5" t="n">
-        <v>-0.017598</v>
-      </c>
-      <c r="P224" s="5" t="n">
-        <v>-0.007323</v>
+        <v>1</v>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -25875,7 +25793,7 @@
       <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Loss on disposal of property and equipment</t>
+          <t>Lease finance charges 9</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -25919,23 +25837,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M225" s="5" t="n">
+        <v>-0.024429</v>
+      </c>
+      <c r="N225" s="5" t="n">
+        <v>-0.021824</v>
+      </c>
+      <c r="O225" s="5" t="n">
+        <v>-0.017598</v>
       </c>
       <c r="P225" s="5" t="n">
-        <v>-0.001659</v>
+        <v>-0.007323</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -25957,7 +25869,7 @@
       <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Flow-through premium recovery 12</t>
+          <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -26011,11 +25923,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O226" s="5" t="n">
-        <v>2.332396</v>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P226" s="5" t="n">
-        <v>2.133046</v>
+        <v>-0.001659</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -26037,14 +25951,10 @@
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Income (loss) before income taxes</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Flow-through premium recovery 12</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -26096,10 +26006,10 @@
         </is>
       </c>
       <c r="O227" s="5" t="n">
-        <v>1.577042</v>
+        <v>2.332396</v>
       </c>
       <c r="P227" s="5" t="n">
-        <v>-0.76849</v>
+        <v>2.133046</v>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
@@ -26121,10 +26031,14 @@
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Income tax recovery/(expense) 11</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>Income (loss) before income taxes</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -26176,10 +26090,10 @@
         </is>
       </c>
       <c r="O228" s="5" t="n">
-        <v>-1.535991</v>
+        <v>1.577042</v>
       </c>
       <c r="P228" s="5" t="n">
-        <v>-0.507831</v>
+        <v>-0.76849</v>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
@@ -26198,19 +26112,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Income (loss) and total comprehensive</t>
-        </is>
-      </c>
+      <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Income (loss) and total comprehensive income (loss) for the year</t>
+          <t>Income tax recovery/(expense) 11</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -26264,10 +26174,10 @@
         </is>
       </c>
       <c r="O229" s="5" t="n">
-        <v>0.041051</v>
+        <v>-1.535991</v>
       </c>
       <c r="P229" s="5" t="n">
-        <v>-1.276321</v>
+        <v>-0.507831</v>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
@@ -26288,15 +26198,19 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Earnings (Loss) per share</t>
+          <t>Income (loss) and total comprehensive</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>- Basic and diluted earnings (loss) per share</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
+          <t>Income (loss) and total comprehensive income (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -26347,13 +26261,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O230" s="5" t="n">
+        <v>0.041051</v>
       </c>
       <c r="P230" s="5" t="n">
-        <v>-8e-08</v>
+        <v>-1.276321</v>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
@@ -26374,19 +26286,15 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Earnings (Loss) per share</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>- Basic</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>- Basic and diluted earnings (loss) per share</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -26432,14 +26340,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N231" s="5" t="n">
-        <v>12.452895</v>
-      </c>
-      <c r="O231" s="5" t="n">
-        <v>14.134202</v>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P231" s="5" t="n">
-        <v>16.258583</v>
+        <v>-8e-08</v>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
@@ -26465,12 +26377,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>- Diluted</t>
+          <t>- Basic</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>DilutedAverageShares</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -26522,7 +26434,7 @@
         <v>12.452895</v>
       </c>
       <c r="O232" s="5" t="n">
-        <v>14.46265</v>
+        <v>14.134202</v>
       </c>
       <c r="P232" s="5" t="n">
         <v>16.258583</v>
@@ -26544,13 +26456,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr"/>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>General exploration</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>- Diluted</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -26596,18 +26516,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N233" s="5" t="n">
+        <v>12.452895</v>
       </c>
       <c r="O233" s="5" t="n">
-        <v>0.001388</v>
-      </c>
-      <c r="P233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14.46265</v>
+      </c>
+      <c r="P233" s="5" t="n">
+        <v>16.258583</v>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
@@ -26629,48 +26545,62 @@
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Office and administration</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E234" s="5" t="n">
-        <v>0.103693</v>
-      </c>
-      <c r="F234" s="5" t="n">
-        <v>0.073606</v>
-      </c>
-      <c r="G234" s="5" t="n">
-        <v>0.07154199999999999</v>
+          <t>General exploration</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I234" s="5" t="n">
-        <v>0.266616</v>
-      </c>
-      <c r="J234" s="5" t="n">
-        <v>0.354387</v>
-      </c>
-      <c r="K234" s="5" t="n">
-        <v>0.344856</v>
-      </c>
-      <c r="L234" s="5" t="n">
-        <v>0.320244</v>
-      </c>
-      <c r="M234" s="5" t="n">
-        <v>0.243775</v>
-      </c>
-      <c r="N234" s="5" t="n">
-        <v>0.134933</v>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O234" s="5" t="n">
-        <v>0.178728</v>
+        <v>0.001388</v>
       </c>
       <c r="P234" t="inlineStr">
         <is>
@@ -26694,67 +26624,51 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>12(c),1</t>
-        </is>
-      </c>
+      <c r="B235" t="inlineStr"/>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Share-based compensation 3</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Office and administration</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E235" s="5" t="n">
+        <v>0.103693</v>
+      </c>
+      <c r="F235" s="5" t="n">
+        <v>0.073606</v>
+      </c>
+      <c r="G235" s="5" t="n">
+        <v>0.07154199999999999</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I235" s="5" t="n">
+        <v>0.266616</v>
+      </c>
+      <c r="J235" s="5" t="n">
+        <v>0.354387</v>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>0.344856</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>0.320244</v>
+      </c>
+      <c r="M235" s="5" t="n">
+        <v>0.243775</v>
       </c>
       <c r="N235" s="5" t="n">
-        <v>1.004589</v>
+        <v>0.134933</v>
       </c>
       <c r="O235" s="5" t="n">
-        <v>0.354998</v>
+        <v>0.178728</v>
       </c>
       <c r="P235" t="inlineStr">
         <is>
@@ -26785,7 +26699,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>12(c),1 total</t>
+          <t>Share-based compensation 3</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -26835,10 +26749,10 @@
         </is>
       </c>
       <c r="N236" s="5" t="n">
-        <v>2.580437</v>
+        <v>1.004589</v>
       </c>
       <c r="O236" s="5" t="n">
-        <v>1.729954</v>
+        <v>0.354998</v>
       </c>
       <c r="P236" t="inlineStr">
         <is>
@@ -26864,12 +26778,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>)                  )</t>
+          <t>12(c),1</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Gain on sale of exploration asset 7</t>
+          <t>12(c),1 total</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -26918,13 +26832,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N237" s="5" t="n">
+        <v>2.580437</v>
       </c>
       <c r="O237" s="5" t="n">
-        <v>1</v>
+        <v>1.729954</v>
       </c>
       <c r="P237" t="inlineStr">
         <is>
@@ -26955,7 +26867,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Lease finance charges 9</t>
+          <t>Gain on sale of exploration asset 7</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -27004,11 +26916,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N238" s="5" t="n">
-        <v>-0.021824</v>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O238" s="5" t="n">
-        <v>-0.017598</v>
+        <v>1</v>
       </c>
       <c r="P238" t="inlineStr">
         <is>
@@ -27039,7 +26953,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Interest income (expense)</t>
+          <t>Lease finance charges 9</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -27089,10 +27003,10 @@
         </is>
       </c>
       <c r="N239" s="5" t="n">
-        <v>-0.003378</v>
+        <v>-0.021824</v>
       </c>
       <c r="O239" s="5" t="n">
-        <v>0.000309</v>
+        <v>-0.017598</v>
       </c>
       <c r="P239" t="inlineStr">
         <is>
@@ -27123,14 +27037,10 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Interest income (expense)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -27177,10 +27087,10 @@
         </is>
       </c>
       <c r="N240" s="5" t="n">
-        <v>-0.006848</v>
+        <v>-0.003378</v>
       </c>
       <c r="O240" s="5" t="n">
-        <v>-0.008111</v>
+        <v>0.000309</v>
       </c>
       <c r="P240" t="inlineStr">
         <is>
@@ -27211,10 +27121,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Flow-through premium recovery 10</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -27261,10 +27175,10 @@
         </is>
       </c>
       <c r="N241" s="5" t="n">
-        <v>1.820424</v>
+        <v>-0.006848</v>
       </c>
       <c r="O241" s="5" t="n">
-        <v>2.332396</v>
+        <v>-0.008111</v>
       </c>
       <c r="P241" t="inlineStr">
         <is>
@@ -27295,7 +27209,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Write-down of exploration and evaluation assets</t>
+          <t>Flow-through premium recovery 10</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -27345,12 +27259,10 @@
         </is>
       </c>
       <c r="N242" s="5" t="n">
-        <v>-0.110018</v>
-      </c>
-      <c r="O242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.820424</v>
+      </c>
+      <c r="O242" s="5" t="n">
+        <v>2.332396</v>
       </c>
       <c r="P242" t="inlineStr">
         <is>
@@ -27381,14 +27293,10 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Income (loss) before income taxes</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Write-down of exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -27435,10 +27343,12 @@
         </is>
       </c>
       <c r="N243" s="5" t="n">
-        <v>-0.902081</v>
-      </c>
-      <c r="O243" s="5" t="n">
-        <v>1.577042</v>
+        <v>-0.110018</v>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
@@ -27464,17 +27374,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Earnings (Loss) per share</t>
+          <t>)                  )</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>- Basic earnings (loss) per share</t>
+          <t>Income (loss) before income taxes</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -27523,12 +27433,10 @@
         </is>
       </c>
       <c r="N244" s="5" t="n">
-        <v>-9e-08</v>
-      </c>
-      <c r="O244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.902081</v>
+      </c>
+      <c r="O244" s="5" t="n">
+        <v>1.577042</v>
       </c>
       <c r="P244" t="inlineStr">
         <is>
@@ -27559,12 +27467,12 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>- Diluted earnings (loss) per share</t>
+          <t>- Basic earnings (loss) per share</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>DilutedEPS</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -27642,13 +27550,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr"/>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Earnings (Loss) per share</t>
+        </is>
+      </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Interest income (expense)</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
+          <t>- Diluted earnings (loss) per share</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -27689,11 +27605,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M246" s="5" t="n">
-        <v>0.013646</v>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N246" s="5" t="n">
-        <v>-0.003378</v>
+        <v>-9e-08</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
@@ -27725,7 +27643,7 @@
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Flow-through premium recovery</t>
+          <t>Interest income (expense)</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -27770,10 +27688,10 @@
         </is>
       </c>
       <c r="M247" s="5" t="n">
-        <v>0.011653</v>
+        <v>0.013646</v>
       </c>
       <c r="N247" s="5" t="n">
-        <v>1.820424</v>
+        <v>-0.003378</v>
       </c>
       <c r="O247" t="inlineStr">
         <is>
@@ -27805,14 +27723,10 @@
       <c r="B248" t="inlineStr"/>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Flow-through premium recovery</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -27853,13 +27767,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M248" s="5" t="n">
+        <v>0.011653</v>
       </c>
       <c r="N248" s="5" t="n">
-        <v>-0.25</v>
+        <v>1.820424</v>
       </c>
       <c r="O248" t="inlineStr">
         <is>
@@ -27888,19 +27800,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Loss per share</t>
-        </is>
-      </c>
+      <c r="B249" t="inlineStr"/>
       <c r="C249" t="inlineStr">
         <is>
-          <t>- Basic and diluted</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -27908,32 +27816,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F249" s="5" t="n">
-        <v>-1.3e-07</v>
-      </c>
-      <c r="G249" s="5" t="n">
-        <v>-5.4e-07</v>
-      </c>
-      <c r="H249" s="5" t="n">
-        <v>-1.2e-07</v>
-      </c>
-      <c r="I249" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="J249" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="K249" s="5" t="n">
-        <v>-4e-07</v>
-      </c>
-      <c r="L249" s="5" t="n">
-        <v>-2.3e-07</v>
-      </c>
-      <c r="M249" s="5" t="n">
-        <v>-1e-07</v>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N249" s="5" t="n">
-        <v>-9e-08</v>
+        <v>-0.25</v>
       </c>
       <c r="O249" t="inlineStr">
         <is>
@@ -27964,7 +27888,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -27972,40 +27896,42 @@
           <t>- Basic and diluted</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F250" s="5" t="n">
-        <v>21.925489</v>
+        <v>-1.3e-07</v>
       </c>
       <c r="G250" s="5" t="n">
-        <v>31.774447</v>
+        <v>-5.4e-07</v>
       </c>
       <c r="H250" s="5" t="n">
-        <v>35.519325</v>
+        <v>-1.2e-07</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>53.21785</v>
+        <v>-4e-08</v>
       </c>
       <c r="J250" s="5" t="n">
-        <v>75.195001</v>
+        <v>-3e-08</v>
       </c>
       <c r="K250" s="5" t="n">
-        <v>81.958581</v>
-      </c>
-      <c r="L250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-07</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>-2.3e-07</v>
       </c>
       <c r="M250" s="5" t="n">
-        <v>10.726087</v>
+        <v>-1e-07</v>
       </c>
       <c r="N250" s="5" t="n">
-        <v>12.452895</v>
+        <v>-9e-08</v>
       </c>
       <c r="O250" t="inlineStr">
         <is>
@@ -28034,60 +27960,50 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr"/>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Depreciation 8</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>- Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F251" s="5" t="n">
+        <v>21.925489</v>
+      </c>
+      <c r="G251" s="5" t="n">
+        <v>31.774447</v>
+      </c>
+      <c r="H251" s="5" t="n">
+        <v>35.519325</v>
+      </c>
+      <c r="I251" s="5" t="n">
+        <v>53.21785</v>
       </c>
       <c r="J251" s="5" t="n">
-        <v>0.014588</v>
+        <v>75.195001</v>
       </c>
       <c r="K251" s="5" t="n">
-        <v>0.027141</v>
-      </c>
-      <c r="L251" s="5" t="n">
-        <v>0.024926</v>
-      </c>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>81.958581</v>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M251" s="5" t="n">
+        <v>10.726087</v>
+      </c>
+      <c r="N251" s="5" t="n">
+        <v>12.452895</v>
       </c>
       <c r="O251" t="inlineStr">
         <is>
@@ -28119,10 +28035,14 @@
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Property investigation expenses</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
+          <t>Depreciation 8</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -28143,19 +28063,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I252" s="5" t="n">
-        <v>0.047831</v>
-      </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J252" s="5" t="n">
+        <v>0.014588</v>
       </c>
       <c r="K252" s="5" t="n">
-        <v>0.006493</v>
+        <v>0.027141</v>
       </c>
       <c r="L252" s="5" t="n">
-        <v>0.008857</v>
+        <v>0.024926</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
@@ -28197,7 +28117,7 @@
       <c r="B253" t="inlineStr"/>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Share-based compensation 12(c),(e), 13</t>
+          <t>Property investigation expenses</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -28221,10 +28141,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I253" s="5" t="n">
+        <v>0.047831</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -28232,10 +28150,10 @@
         </is>
       </c>
       <c r="K253" s="5" t="n">
-        <v>1.094447</v>
+        <v>0.006493</v>
       </c>
       <c r="L253" s="5" t="n">
-        <v>0.855535</v>
+        <v>0.008857</v>
       </c>
       <c r="M253" t="inlineStr">
         <is>
@@ -28277,37 +28195,45 @@
       <c r="B254" t="inlineStr"/>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Finance income</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E254" s="5" t="n">
-        <v>0.098442</v>
-      </c>
-      <c r="F254" s="5" t="n">
-        <v>0.047494</v>
-      </c>
-      <c r="G254" s="5" t="n">
-        <v>0.029967</v>
-      </c>
-      <c r="H254" s="5" t="n">
-        <v>0.003134</v>
-      </c>
-      <c r="I254" s="5" t="n">
-        <v>0.006195</v>
-      </c>
-      <c r="J254" s="5" t="n">
-        <v>0.023278</v>
+          <t>Share-based compensation 12(c),(e), 13</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K254" s="5" t="n">
-        <v>0.034675</v>
+        <v>1.094447</v>
       </c>
       <c r="L254" s="5" t="n">
-        <v>0.034473</v>
+        <v>0.855535</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
@@ -28349,47 +28275,37 @@
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Realized loss on sale of marketable securities 3, 7</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Finance income</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E255" s="5" t="n">
+        <v>0.098442</v>
+      </c>
+      <c r="F255" s="5" t="n">
+        <v>0.047494</v>
+      </c>
+      <c r="G255" s="5" t="n">
+        <v>0.029967</v>
+      </c>
+      <c r="H255" s="5" t="n">
+        <v>0.003134</v>
+      </c>
+      <c r="I255" s="5" t="n">
+        <v>0.006195</v>
+      </c>
+      <c r="J255" s="5" t="n">
+        <v>0.023278</v>
       </c>
       <c r="K255" s="5" t="n">
-        <v>-0.247171</v>
-      </c>
-      <c r="L255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.034675</v>
+      </c>
+      <c r="L255" s="5" t="n">
+        <v>0.034473</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
@@ -28431,7 +28347,7 @@
       <c r="B256" t="inlineStr"/>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation assets 9</t>
+          <t>Realized loss on sale of marketable securities 3, 7</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -28466,10 +28382,12 @@
         </is>
       </c>
       <c r="K256" s="5" t="n">
-        <v>-0.417794</v>
-      </c>
-      <c r="L256" s="5" t="n">
-        <v>-0.157253</v>
+        <v>-0.247171</v>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
@@ -28511,14 +28429,10 @@
       <c r="B257" t="inlineStr"/>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Write-off of exploration and evaluation assets 9</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -28544,14 +28458,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J257" s="5" t="n">
-        <v>-2.021142</v>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K257" s="5" t="n">
-        <v>-3.287153</v>
+        <v>-0.417794</v>
       </c>
       <c r="L257" s="5" t="n">
-        <v>-1.996753</v>
+        <v>-0.157253</v>
       </c>
       <c r="M257" t="inlineStr">
         <is>
@@ -28590,17 +28506,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
+      <c r="B258" t="inlineStr"/>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Realized loss on sale of marketable securities 3, 7</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr"/>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -28626,18 +28542,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J258" s="5" t="n">
+        <v>-2.021142</v>
+      </c>
+      <c r="K258" s="5" t="n">
+        <v>-3.287153</v>
       </c>
       <c r="L258" s="5" t="n">
-        <v>-0.353995</v>
+        <v>-1.996753</v>
       </c>
       <c r="M258" t="inlineStr">
         <is>
@@ -28683,7 +28595,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Transfer from unrealized loss to realized loss on sale</t>
+          <t>Realized loss on sale of marketable securities 3, 7</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -28717,11 +28629,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K259" s="5" t="n">
-        <v>0.247171</v>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L259" s="5" t="n">
-        <v>0.40092</v>
+        <v>-0.353995</v>
       </c>
       <c r="M259" t="inlineStr">
         <is>
@@ -28767,7 +28681,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on marketable securities 3, 7</t>
+          <t>Transfer from unrealized loss to realized loss on sale</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -28802,12 +28716,10 @@
         </is>
       </c>
       <c r="K260" s="5" t="n">
-        <v>-0.648091</v>
-      </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.247171</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>0.40092</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
@@ -28848,19 +28760,15 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>of marketable securities</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) for the year</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Unrealized gain (loss) on marketable securities 3, 7</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -28892,10 +28800,12 @@
         </is>
       </c>
       <c r="K261" s="5" t="n">
-        <v>-0.40092</v>
-      </c>
-      <c r="L261" s="5" t="n">
-        <v>0.046925</v>
+        <v>-0.648091</v>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
@@ -28941,7 +28851,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the year</t>
+          <t>Comprehensive income (loss) for the year</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -28980,10 +28890,10 @@
         </is>
       </c>
       <c r="K262" s="5" t="n">
-        <v>-3.688073</v>
+        <v>-0.40092</v>
       </c>
       <c r="L262" s="5" t="n">
-        <v>-1.949828</v>
+        <v>0.046925</v>
       </c>
       <c r="M262" t="inlineStr">
         <is>
@@ -29024,15 +28934,19 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding1</t>
+          <t>of marketable securities</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>- Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
+          <t>Total comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -29064,10 +28978,10 @@
         </is>
       </c>
       <c r="K263" s="5" t="n">
-        <v>8.195857999999999</v>
+        <v>-3.688073</v>
       </c>
       <c r="L263" s="5" t="n">
-        <v>8.613714</v>
+        <v>-1.949828</v>
       </c>
       <c r="M263" t="inlineStr">
         <is>
@@ -29106,10 +29020,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr"/>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding1</t>
+        </is>
+      </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Share-based compensation 12c, 13</t>
+          <t>- Basic and diluted</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -29138,16 +29056,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J264" s="5" t="n">
-        <v>0.311559</v>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K264" s="5" t="n">
-        <v>1.094447</v>
-      </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.195857999999999</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>8.613714</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
@@ -29189,7 +29107,7 @@
       <c r="B265" t="inlineStr"/>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Loss on sale of marketable securities 7</t>
+          <t>Share-based compensation 12c, 13</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -29218,13 +29136,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J265" s="5" t="n">
+        <v>0.311559</v>
       </c>
       <c r="K265" s="5" t="n">
-        <v>-0.247171</v>
+        <v>1.094447</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -29268,14 +29184,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Items that maybe reclassified subsequently to loss</t>
-        </is>
-      </c>
+      <c r="B266" t="inlineStr"/>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Unrealized loss on available for sale financial assets 7</t>
+          <t>Loss on sale of marketable securities 7</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -29310,7 +29222,7 @@
         </is>
       </c>
       <c r="K266" s="5" t="n">
-        <v>-0.648091</v>
+        <v>-0.247171</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -29356,12 +29268,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Transfer of realized loss on sale of marketable</t>
+          <t>Items that maybe reclassified subsequently to loss</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Transfer of realized loss on sale of marketable securities 7</t>
+          <t>Unrealized loss on available for sale financial assets 7</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -29396,7 +29308,7 @@
         </is>
       </c>
       <c r="K267" s="5" t="n">
-        <v>0.247171</v>
+        <v>-0.648091</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -29447,14 +29359,10 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Transfer of realized loss on sale of marketable securities 7</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -29480,11 +29388,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J268" s="5" t="n">
-        <v>-2.021142</v>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K268" s="5" t="n">
-        <v>-3.688073</v>
+        <v>0.247171</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -29528,15 +29438,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr"/>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Transfer of realized loss on sale of marketable</t>
+        </is>
+      </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Depreciation 7</t>
+          <t>Comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -29549,22 +29463,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G269" s="5" t="n">
-        <v>0.02934</v>
-      </c>
-      <c r="H269" s="5" t="n">
-        <v>0.023149</v>
-      </c>
-      <c r="I269" s="5" t="n">
-        <v>0.00971</v>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J269" s="5" t="n">
-        <v>0.014588</v>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.021142</v>
+      </c>
+      <c r="K269" s="5" t="n">
+        <v>-3.688073</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -29611,12 +29529,12 @@
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Management and consulting fees 11</t>
+          <t>Depreciation 7</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -29629,21 +29547,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G270" s="5" t="n">
+        <v>0.02934</v>
+      </c>
+      <c r="H270" s="5" t="n">
+        <v>0.023149</v>
       </c>
       <c r="I270" s="5" t="n">
-        <v>0.383074</v>
+        <v>0.00971</v>
       </c>
       <c r="J270" s="5" t="n">
-        <v>0.333329</v>
+        <v>0.014588</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
@@ -29695,12 +29609,12 @@
       <c r="B271" t="inlineStr"/>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Professional fees 11</t>
+          <t>Management and consulting fees 11</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -29724,10 +29638,10 @@
         </is>
       </c>
       <c r="I271" s="5" t="n">
-        <v>0.114352</v>
+        <v>0.383074</v>
       </c>
       <c r="J271" s="5" t="n">
-        <v>0.130982</v>
+        <v>0.333329</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
@@ -29779,10 +29693,14 @@
       <c r="B272" t="inlineStr"/>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Share-based compensation 10c, 11</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr"/>
+          <t>Professional fees 11</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -29804,10 +29722,10 @@
         </is>
       </c>
       <c r="I272" s="5" t="n">
-        <v>0.461539</v>
+        <v>0.114352</v>
       </c>
       <c r="J272" s="5" t="n">
-        <v>0.311559</v>
+        <v>0.130982</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
@@ -29859,7 +29777,7 @@
       <c r="B273" t="inlineStr"/>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable 9</t>
+          <t>Share-based compensation 10c, 11</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -29884,12 +29802,10 @@
         </is>
       </c>
       <c r="I273" s="5" t="n">
-        <v>0.1422</v>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.461539</v>
+      </c>
+      <c r="J273" s="5" t="n">
+        <v>0.311559</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
@@ -29941,14 +29857,10 @@
       <c r="B274" t="inlineStr"/>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on settlement of accounts payable 9</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -29959,17 +29871,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G274" s="5" t="n">
-        <v>-17.194821</v>
-      </c>
-      <c r="H274" s="5" t="n">
-        <v>-4.389963</v>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I274" s="5" t="n">
-        <v>-1.983638</v>
-      </c>
-      <c r="J274" s="5" t="n">
-        <v>-2.021142</v>
+        <v>0.1422</v>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
@@ -30021,33 +29939,35 @@
       <c r="B275" t="inlineStr"/>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Audit and accounting 10</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>Loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F275" s="5" t="n">
-        <v>0.157565</v>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G275" s="5" t="n">
-        <v>0.113176</v>
+        <v>-17.194821</v>
       </c>
       <c r="H275" s="5" t="n">
-        <v>0.06578100000000001</v>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.389963</v>
+      </c>
+      <c r="I275" s="5" t="n">
+        <v>-1.983638</v>
+      </c>
+      <c r="J275" s="5" t="n">
+        <v>-2.021142</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
@@ -30099,27 +30019,23 @@
       <c r="B276" t="inlineStr"/>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Consulting fees 10</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Audit and accounting 10</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F276" s="5" t="n">
-        <v>0.059985</v>
+        <v>0.157565</v>
       </c>
       <c r="G276" s="5" t="n">
-        <v>0.02303</v>
+        <v>0.113176</v>
       </c>
       <c r="H276" s="5" t="n">
-        <v>0.127239</v>
+        <v>0.06578100000000001</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -30181,21 +30097,27 @@
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Insurance expense</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
-      <c r="E277" s="5" t="n">
-        <v>0.036269</v>
+          <t>Consulting fees 10</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F277" s="5" t="n">
-        <v>0.028464</v>
+        <v>0.059985</v>
       </c>
       <c r="G277" s="5" t="n">
-        <v>0.027273</v>
+        <v>0.02303</v>
       </c>
       <c r="H277" s="5" t="n">
-        <v>0.027998</v>
+        <v>0.127239</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -30257,25 +30179,21 @@
       <c r="B278" t="inlineStr"/>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Legal fees</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Insurance expense</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" s="5" t="n">
-        <v>0.10643</v>
+        <v>0.036269</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>0.07232</v>
+        <v>0.028464</v>
       </c>
       <c r="G278" s="5" t="n">
-        <v>0.07058499999999999</v>
+        <v>0.027273</v>
       </c>
       <c r="H278" s="5" t="n">
-        <v>0.028349</v>
+        <v>0.027998</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -30337,21 +30255,25 @@
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Listing and sustaining fees</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>Legal fees</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E279" s="5" t="n">
-        <v>0.01797</v>
+        <v>0.10643</v>
       </c>
       <c r="F279" s="5" t="n">
-        <v>0.025156</v>
+        <v>0.07232</v>
       </c>
       <c r="G279" s="5" t="n">
-        <v>0.021758</v>
+        <v>0.07058499999999999</v>
       </c>
       <c r="H279" s="5" t="n">
-        <v>0.026085</v>
+        <v>0.028349</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -30413,21 +30335,21 @@
       <c r="B280" t="inlineStr"/>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Property expenses</t>
+          <t>Listing and sustaining fees</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
       <c r="E280" s="5" t="n">
-        <v>0.12915</v>
+        <v>0.01797</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>0.105231</v>
+        <v>0.025156</v>
       </c>
       <c r="G280" s="5" t="n">
-        <v>0.024751</v>
+        <v>0.021758</v>
       </c>
       <c r="H280" s="5" t="n">
-        <v>0.011506</v>
+        <v>0.026085</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -30489,25 +30411,21 @@
       <c r="B281" t="inlineStr"/>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Office, administration and rent 10</t>
+          <t>Property expenses</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E281" s="5" t="n">
+        <v>0.12915</v>
+      </c>
+      <c r="F281" s="5" t="n">
+        <v>0.105231</v>
       </c>
       <c r="G281" s="5" t="n">
-        <v>0.136838</v>
+        <v>0.024751</v>
       </c>
       <c r="H281" s="5" t="n">
-        <v>0.128868</v>
+        <v>0.011506</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -30569,7 +30487,7 @@
       <c r="B282" t="inlineStr"/>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Salaries</t>
+          <t>Office, administration and rent 10</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -30584,10 +30502,10 @@
         </is>
       </c>
       <c r="G282" s="5" t="n">
-        <v>0.560222</v>
+        <v>0.136838</v>
       </c>
       <c r="H282" s="5" t="n">
-        <v>0.28578</v>
+        <v>0.128868</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -30649,7 +30567,7 @@
       <c r="B283" t="inlineStr"/>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Shareholder engagement</t>
+          <t>Salaries</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -30664,10 +30582,10 @@
         </is>
       </c>
       <c r="G283" s="5" t="n">
-        <v>0.153009</v>
+        <v>0.560222</v>
       </c>
       <c r="H283" s="5" t="n">
-        <v>0.260257</v>
+        <v>0.28578</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -30729,7 +30647,7 @@
       <c r="B284" t="inlineStr"/>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Share-based compensation 9</t>
+          <t>Shareholder engagement</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -30744,10 +30662,10 @@
         </is>
       </c>
       <c r="G284" s="5" t="n">
-        <v>0.347878</v>
+        <v>0.153009</v>
       </c>
       <c r="H284" s="5" t="n">
-        <v>0.205781</v>
+        <v>0.260257</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -30809,25 +30727,25 @@
       <c r="B285" t="inlineStr"/>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Transfer agent</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E285" s="5" t="n">
-        <v>0.016418</v>
-      </c>
-      <c r="F285" s="5" t="n">
-        <v>0.010759</v>
+          <t>Share-based compensation 9</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G285" s="5" t="n">
-        <v>0.010579</v>
+        <v>0.347878</v>
       </c>
       <c r="H285" s="5" t="n">
-        <v>0.009795999999999999</v>
+        <v>0.205781</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -30889,25 +30807,25 @@
       <c r="B286" t="inlineStr"/>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Transfer agent</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E286" s="5" t="n">
-        <v>0.041244</v>
+        <v>0.016418</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>0.021001</v>
+        <v>0.010759</v>
       </c>
       <c r="G286" s="5" t="n">
-        <v>0.024972</v>
+        <v>0.010579</v>
       </c>
       <c r="H286" s="5" t="n">
-        <v>0.042344</v>
+        <v>0.009795999999999999</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -30969,25 +30887,25 @@
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Write off of equipment 7</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr"/>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E287" s="5" t="n">
+        <v>0.041244</v>
+      </c>
+      <c r="F287" s="5" t="n">
+        <v>0.021001</v>
       </c>
       <c r="G287" s="5" t="n">
-        <v>-0.00552</v>
+        <v>0.024972</v>
       </c>
       <c r="H287" s="5" t="n">
-        <v>-0.032095</v>
+        <v>0.042344</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
@@ -31049,7 +30967,7 @@
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 8</t>
+          <t>Write off of equipment 7</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -31064,10 +30982,10 @@
         </is>
       </c>
       <c r="G288" s="5" t="n">
-        <v>-21.525857</v>
+        <v>-0.00552</v>
       </c>
       <c r="H288" s="5" t="n">
-        <v>-3.536375</v>
+        <v>-0.032095</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
@@ -31129,7 +31047,7 @@
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery 11</t>
+          <t>Impairment of exploration and evaluation assets 8</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -31144,10 +31062,10 @@
         </is>
       </c>
       <c r="G289" s="5" t="n">
-        <v>5.85</v>
+        <v>-21.525857</v>
       </c>
       <c r="H289" s="5" t="n">
-        <v>0.418306</v>
+        <v>-3.536375</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
@@ -31209,25 +31127,29 @@
       <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Property investigation costs</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" s="5" t="n">
-        <v>0.172369</v>
-      </c>
-      <c r="F290" s="5" t="n">
-        <v>0.009606999999999999</v>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deferred income tax recovery 11</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G290" s="5" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="H290" s="5" t="n">
+        <v>0.418306</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
@@ -31289,18 +31211,20 @@
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Office rent</t>
+          <t>Property investigation costs</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" s="5" t="n">
-        <v>0.036831</v>
+        <v>0.172369</v>
       </c>
       <c r="F291" s="5" t="n">
-        <v>0.070476</v>
-      </c>
-      <c r="G291" s="5" t="n">
-        <v>0.06529600000000001</v>
+        <v>0.009606999999999999</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -31367,20 +31291,18 @@
       <c r="B292" t="inlineStr"/>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Salaries 10</t>
+          <t>Office rent</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E292" s="5" t="n">
+        <v>0.036831</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>0.669022</v>
+        <v>0.070476</v>
       </c>
       <c r="G292" s="5" t="n">
-        <v>0.560222</v>
+        <v>0.06529600000000001</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -31447,18 +31369,20 @@
       <c r="B293" t="inlineStr"/>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Shareholder relations and news releases</t>
+          <t>Salaries 10</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
-      <c r="E293" s="5" t="n">
-        <v>0.149968</v>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F293" s="5" t="n">
-        <v>0.111264</v>
+        <v>0.669022</v>
       </c>
       <c r="G293" s="5" t="n">
-        <v>0.153009</v>
+        <v>0.560222</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -31525,20 +31449,18 @@
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Share-based compensation 8</t>
+          <t>Shareholder relations and news releases</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E294" s="5" t="n">
+        <v>0.149968</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>0.275998</v>
+        <v>0.111264</v>
       </c>
       <c r="G294" s="5" t="n">
-        <v>0.347878</v>
+        <v>0.153009</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -31605,24 +31527,20 @@
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Dividend income</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>DividendIncome</t>
-        </is>
-      </c>
-      <c r="E295" s="5" t="n">
-        <v>0.016</v>
+          <t>Share-based compensation 8</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F295" s="5" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.275998</v>
+      </c>
+      <c r="G295" s="5" t="n">
+        <v>0.347878</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -31689,22 +31607,24 @@
       <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Write off of equipment 6</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G296" s="5" t="n">
-        <v>-0.00552</v>
+          <t>Dividend income</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>DividendIncome</t>
+        </is>
+      </c>
+      <c r="E296" s="5" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F296" s="5" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -31768,14 +31688,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Write off and impairment of exploration and evaluation</t>
-        </is>
-      </c>
+      <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Write off and impairment of exploration and evaluation assets 7</t>
+          <t>Write off of equipment 6</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -31784,11 +31700,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F297" s="5" t="n">
-        <v>-1.122556</v>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G297" s="5" t="n">
-        <v>-21.525857</v>
+        <v>-0.00552</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -31859,7 +31777,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Write off and impairment of exploration and evaluation total</t>
+          <t>Write off and impairment of exploration and evaluation assets 7</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -31869,10 +31787,10 @@
         </is>
       </c>
       <c r="F298" s="5" t="n">
-        <v>-2.794972</v>
+        <v>-1.122556</v>
       </c>
       <c r="G298" s="5" t="n">
-        <v>-23.044821</v>
+        <v>-21.525857</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -31943,7 +31861,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery 11</t>
+          <t>Write off and impairment of exploration and evaluation total</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -31953,10 +31871,10 @@
         </is>
       </c>
       <c r="F299" s="5" t="n">
-        <v>0.008092999999999999</v>
+        <v>-2.794972</v>
       </c>
       <c r="G299" s="5" t="n">
-        <v>5.85</v>
+        <v>-23.044821</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -32027,12 +31945,12 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
+          <t>Deferred income tax recovery 11</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -32041,10 +31959,10 @@
         </is>
       </c>
       <c r="F300" s="5" t="n">
-        <v>-2.786879</v>
+        <v>0.008092999999999999</v>
       </c>
       <c r="G300" s="5" t="n">
-        <v>-17.194821</v>
+        <v>5.85</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -32110,27 +32028,29 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Write off and impairment of exploration and evaluation</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Change in fair value of restricted investments</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F301" s="5" t="n">
-        <v>0.0896</v>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.786879</v>
+      </c>
+      <c r="G301" s="5" t="n">
+        <v>-17.194821</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
@@ -32201,24 +32121,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Change in fair value of restricted investments</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F302" s="5" t="n">
-        <v>-2.697279</v>
-      </c>
-      <c r="G302" s="5" t="n">
-        <v>-17.194821</v>
+        <v>0.0896</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
@@ -32282,23 +32200,31 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr"/>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Audit and accounting (Note 10) $</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
-      <c r="E303" s="5" t="n">
-        <v>0.189654</v>
+          <t>Total comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F303" s="5" t="n">
-        <v>0.157565</v>
-      </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.697279</v>
+      </c>
+      <c r="G303" s="5" t="n">
+        <v>-17.194821</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
@@ -32365,19 +32291,15 @@
       <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Audit and accounting (Note 10) $</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" s="5" t="n">
-        <v>0.166016</v>
+        <v>0.189654</v>
       </c>
       <c r="F304" s="5" t="n">
-        <v>0.059985</v>
+        <v>0.157565</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
@@ -32449,19 +32371,19 @@
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Equipment depreciation (Note 6)</t>
+          <t>Consulting fees</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E305" s="5" t="n">
-        <v>0.027905</v>
+        <v>0.166016</v>
       </c>
       <c r="F305" s="5" t="n">
-        <v>0.033656</v>
+        <v>0.059985</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
@@ -32533,15 +32455,19 @@
       <c r="B306" t="inlineStr"/>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Salaries (Note 10)</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>Equipment depreciation (Note 6)</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E306" s="5" t="n">
-        <v>0.738734</v>
+        <v>0.027905</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>0.669022</v>
+        <v>0.033656</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
@@ -32613,15 +32539,15 @@
       <c r="B307" t="inlineStr"/>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 10)</t>
+          <t>Salaries (Note 10)</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
       <c r="E307" s="5" t="n">
-        <v>0.074563</v>
+        <v>0.738734</v>
       </c>
       <c r="F307" s="5" t="n">
-        <v>0.275998</v>
+        <v>0.669022</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -32693,15 +32619,15 @@
       <c r="B308" t="inlineStr"/>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation assets (Note 5)</t>
+          <t>Share-based compensation (Note 10)</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
       <c r="E308" s="5" t="n">
-        <v>-2.982123</v>
+        <v>0.074563</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>-1.122556</v>
+        <v>0.275998</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
@@ -32773,19 +32699,15 @@
       <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Loss before income tax</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Write-off of exploration and evaluation assets (Note 5)</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
       <c r="E309" s="5" t="n">
-        <v>-4.874895</v>
+        <v>-2.982123</v>
       </c>
       <c r="F309" s="5" t="n">
-        <v>-2.794972</v>
+        <v>-1.122556</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -32857,15 +32779,19 @@
       <c r="B310" t="inlineStr"/>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (Note 13)</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>Loss before income tax</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E310" s="5" t="n">
-        <v>1.196</v>
+        <v>-4.874895</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>0.008092999999999999</v>
+        <v>-2.794972</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
@@ -32937,19 +32863,19 @@
       <c r="B311" t="inlineStr"/>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Loss for the year $</t>
+          <t>Deferred income tax recovery (Note 13)</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E311" s="5" t="n">
-        <v>-3.678895</v>
+        <v>1.196</v>
       </c>
       <c r="F311" s="5" t="n">
-        <v>-2.786879</v>
+        <v>0.008092999999999999</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
@@ -33021,15 +32947,19 @@
       <c r="B312" t="inlineStr"/>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Change in fair value of restricted investment $</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>Loss for the year $</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E312" s="5" t="n">
-        <v>0.43665</v>
+        <v>-3.678895</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>0.0896</v>
+        <v>-2.786879</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -33101,19 +33031,15 @@
       <c r="B313" t="inlineStr"/>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Change in fair value of restricted investment $</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
       <c r="E313" s="5" t="n">
-        <v>-3.242245</v>
+        <v>0.43665</v>
       </c>
       <c r="F313" s="5" t="n">
-        <v>-2.697279</v>
+        <v>0.0896</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
@@ -33185,19 +33111,19 @@
       <c r="B314" t="inlineStr"/>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E314" s="5" t="n">
-        <v>-2e-07</v>
+        <v>-3.242245</v>
       </c>
       <c r="F314" s="5" t="n">
-        <v>-1.3e-07</v>
+        <v>-2.697279</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -33269,19 +33195,19 @@
       <c r="B315" t="inlineStr"/>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Basic and diluted loss per common share $</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E315" s="5" t="n">
-        <v>18.117653</v>
+        <v>-2e-07</v>
       </c>
       <c r="F315" s="5" t="n">
-        <v>21.925489</v>
+        <v>-1.3e-07</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
@@ -33350,24 +33276,22 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Shares         Amount         Advance                                      Deficit            Total</t>
-        </is>
-      </c>
+      <c r="B316" t="inlineStr"/>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Stock options exercised 168,302 192,974 - (119,111) -</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E316" s="5" t="n">
-        <v>0.073863</v>
-      </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18.117653</v>
+      </c>
+      <c r="F316" s="5" t="n">
+        <v>21.925489</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
@@ -33443,12 +33367,12 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Private placement – flow through shares 1,489,100 1,414,645 - - -</t>
+          <t>Stock options exercised 168,302 192,974 - (119,111) -</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
       <c r="E317" s="5" t="n">
-        <v>1.414645</v>
+        <v>0.073863</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33529,12 +33453,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Flow through share premium - (223,365) - - -</t>
+          <t>Private placement – flow through shares 1,489,100 1,414,645 - - -</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" s="5" t="n">
-        <v>-0.223365</v>
+        <v>1.414645</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33615,12 +33539,12 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Shares issue costs – cash (net of taxes) - (7,720) - - -</t>
+          <t>Flow through share premium - (223,365) - - -</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" s="5" t="n">
-        <v>-0.00772</v>
+        <v>-0.223365</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33701,14 +33625,12 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Share issue costs – agent warrants - (2,850) - 2,850 -</t>
+          <t>Shares issue costs – cash (net of taxes) - (7,720) - - -</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E320" s="5" t="n">
+        <v>-0.00772</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33789,12 +33711,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation asset 25,000 7,500 - - -</t>
+          <t>Share issue costs – agent warrants - (2,850) - 2,850 -</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
-      <c r="E321" s="5" t="n">
-        <v>0.0075</v>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33875,12 +33799,12 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Subscriptions received in advance - - 690,000 - -</t>
+          <t>Shares issued for exploration and evaluation asset 25,000 7,500 - - -</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
       <c r="E322" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.0075</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33961,12 +33885,12 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Share-based compensation - - - 74,563 -</t>
+          <t>Subscriptions received in advance - - 690,000 - -</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" s="5" t="n">
-        <v>0.074563</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -34047,12 +33971,12 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Fair value adjustment of securities - - - - 436,650</t>
+          <t>Share-based compensation - - - 74,563 -</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" s="5" t="n">
-        <v>0.43665</v>
+        <v>0.074563</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34133,19 +34057,17 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Loss for the year - - - - -</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Fair value adjustment of securities - - - - 436,650</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
       <c r="E325" s="5" t="n">
-        <v>-3.678895</v>
-      </c>
-      <c r="F325" s="5" t="n">
-        <v>-3.678895</v>
+        <v>0.43665</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
@@ -34221,15 +34143,19 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Balance, September 30, 2012 18,562,352 40,053,541 690,000 3,742,064 (89,600)</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
+          <t>Loss for the year - - - - -</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E326" s="5" t="n">
-        <v>30.36761</v>
+        <v>-3.678895</v>
       </c>
       <c r="F326" s="5" t="n">
-        <v>-14.028395</v>
+        <v>-3.678895</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
@@ -34305,17 +34231,15 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Private placement – flow through shares 10,765,000 2,046,000 (690,000) - -</t>
+          <t>Balance, September 30, 2012 18,562,352 40,053,541 690,000 3,742,064 (89,600)</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
       <c r="E327" s="5" t="n">
-        <v>1.356</v>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>30.36761</v>
+      </c>
+      <c r="F327" s="5" t="n">
+        <v>-14.028395</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
@@ -34391,12 +34315,12 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Shares issue costs – cash (net of taxes) - (99,650) - - -</t>
+          <t>Private placement – flow through shares 10,765,000 2,046,000 (690,000) - -</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
       <c r="E328" s="5" t="n">
-        <v>-0.09965</v>
+        <v>1.356</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34477,12 +34401,12 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation asset 460,000 53,000 - - -</t>
+          <t>Shares issue costs – cash (net of taxes) - (99,650) - - -</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
       <c r="E329" s="5" t="n">
-        <v>0.053</v>
+        <v>-0.09965</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34563,12 +34487,12 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Subscriptions received in advance - - 383,950 - -</t>
+          <t>Shares issued for exploration and evaluation asset 460,000 53,000 - - -</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
       <c r="E330" s="5" t="n">
-        <v>0.38395</v>
+        <v>0.053</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34649,12 +34573,12 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Share-based compensation - - - 275,998 -</t>
+          <t>Subscriptions received in advance - - 383,950 - -</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
       <c r="E331" s="5" t="n">
-        <v>0.275998</v>
+        <v>0.38395</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34735,74 +34659,160 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Fair value adjustment of securities - - - - 89,600</t>
+          <t>Share-based compensation - - - 275,998 -</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
       <c r="E332" s="5" t="n">
+        <v>0.275998</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Shares         Amount         Advance                                      Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Fair value adjustment of securities - - - - 89,600</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" s="5" t="n">
         <v>0.0896</v>
       </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R332" t="inlineStr">
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
         <is>
           <t>-</t>
         </is>
